--- a/artfynd/A 9945-2021 artfynd.xlsx
+++ b/artfynd/A 9945-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122034654</v>
       </c>
       <c r="B2" t="n">
-        <v>56619</v>
+        <v>56624</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 9945-2021 artfynd.xlsx
+++ b/artfynd/A 9945-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -787,6 +787,234 @@
           <t>ESN0033_Björksättra_häckfågelinventering_2024</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129219004</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hökärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>671041</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6562502</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Verkade hamstra  föda i hålighet på  torraka</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129219014</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hökärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>671147</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6562576</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>En del av de verkade vara i meståg</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9945-2021 artfynd.xlsx
+++ b/artfynd/A 9945-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1016,6 +1016,721 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129219854</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57333</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102966</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Gråtrut</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Larus argentatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Pontoppidan, 1763</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hökärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>671041</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6562502</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129219868</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58153</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Hökärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>671041</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6562502</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129219865</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57883</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hökärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>671041</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6562502</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129219866</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58093</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hökärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>671041</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6562502</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129219860</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57853</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Hökärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>671041</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6562502</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>129219856</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100048</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mindre hackspett</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dryobates minor</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Hökärr, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>671147</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6562576</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Huddinge</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>09:43</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Verkade vara i meståg</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Gransjön</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 9945-2021 artfynd.xlsx
+++ b/artfynd/A 9945-2021 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>129219004</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129219014</v>
       </c>
       <c r="B4" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129219854</v>
       </c>
       <c r="B5" t="n">
-        <v>57333</v>
+        <v>57335</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129219868</v>
       </c>
       <c r="B6" t="n">
-        <v>58153</v>
+        <v>58155</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>129219865</v>
       </c>
       <c r="B7" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>129219866</v>
       </c>
       <c r="B8" t="n">
-        <v>58093</v>
+        <v>58095</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>129219860</v>
       </c>
       <c r="B9" t="n">
-        <v>57853</v>
+        <v>57855</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>129219856</v>
       </c>
       <c r="B10" t="n">
-        <v>57736</v>
+        <v>57738</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 9945-2021 artfynd.xlsx
+++ b/artfynd/A 9945-2021 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>129219004</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129219014</v>
       </c>
       <c r="B4" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129219854</v>
       </c>
       <c r="B5" t="n">
-        <v>57335</v>
+        <v>57337</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129219868</v>
       </c>
       <c r="B6" t="n">
-        <v>58155</v>
+        <v>58157</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>129219865</v>
       </c>
       <c r="B7" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>129219866</v>
       </c>
       <c r="B8" t="n">
-        <v>58095</v>
+        <v>58097</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>129219860</v>
       </c>
       <c r="B9" t="n">
-        <v>57855</v>
+        <v>57857</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>129219856</v>
       </c>
       <c r="B10" t="n">
-        <v>57738</v>
+        <v>57740</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 9945-2021 artfynd.xlsx
+++ b/artfynd/A 9945-2021 artfynd.xlsx
@@ -793,7 +793,7 @@
         <v>129219004</v>
       </c>
       <c r="B3" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -911,7 +911,7 @@
         <v>129219014</v>
       </c>
       <c r="B4" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1021,7 +1021,7 @@
         <v>129219854</v>
       </c>
       <c r="B5" t="n">
-        <v>57337</v>
+        <v>57340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>129219868</v>
       </c>
       <c r="B6" t="n">
-        <v>58157</v>
+        <v>58160</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1259,7 +1259,7 @@
         <v>129219865</v>
       </c>
       <c r="B7" t="n">
-        <v>57887</v>
+        <v>57890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>129219866</v>
       </c>
       <c r="B8" t="n">
-        <v>58097</v>
+        <v>58100</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
         <v>129219860</v>
       </c>
       <c r="B9" t="n">
-        <v>57857</v>
+        <v>57860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1608,7 +1608,7 @@
         <v>129219856</v>
       </c>
       <c r="B10" t="n">
-        <v>57740</v>
+        <v>57743</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
